--- a/appointment_forms/047_online_reputation_management_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/047_online_reputation_management_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'09:00-11:00'}</t>
+          <t>09:00-11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '09:00-11:00'}</t>
+          <t>09:00-11:00</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'11:00-13:00'}</t>
+          <t>11:00-13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '11:00-13:00'}</t>
+          <t>11:00-13:00</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'14:00-16:00'}</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '14:00-16:00'}</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'16:00-18:00'}</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '16:00-18:00'}</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
